--- a/asset/source/9.xlsx
+++ b/asset/source/9.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="72" uniqueCount="39">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="76" uniqueCount="40">
   <si>
     <t>Part report</t>
   </si>
@@ -131,6 +131,9 @@
   </si>
   <si>
     <t>A5</t>
+  </si>
+  <si>
+    <t>A6</t>
   </si>
 </sst>
 </file>
@@ -1397,13 +1400,30 @@
       </c>
     </row>
     <row r="28" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="B28" s="7"/>
-      <c r="C28" s="7"/>
-      <c r="D28" s="7"/>
-      <c r="E28" s="7"/>
-      <c r="F28" s="7"/>
-      <c r="G28" s="7"/>
-      <c r="H28" s="7"/>
+      <c r="A28">
+        <v>13</v>
+      </c>
+      <c r="B28" s="7" t="s">
+        <v>39</v>
+      </c>
+      <c r="C28" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="D28" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="E28" s="7">
+        <v>94.46</v>
+      </c>
+      <c r="F28" s="7">
+        <v>0.3</v>
+      </c>
+      <c r="G28" s="7">
+        <v>-0.3</v>
+      </c>
+      <c r="H28" s="7" t="s">
+        <v>25</v>
+      </c>
     </row>
     <row r="29" spans="1:8" x14ac:dyDescent="0.25">
       <c r="B29" s="7"/>

--- a/asset/source/9.xlsx
+++ b/asset/source/9.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="9302"/>
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="124226"/>
   <bookViews>
-    <workbookView xWindow="3120" yWindow="3120" windowWidth="14400" windowHeight="10665"/>
+    <workbookView xWindow="3120" yWindow="3120" windowWidth="14400" windowHeight="8730"/>
   </bookViews>
   <sheets>
     <sheet name="364" sheetId="1" r:id="rId1"/>
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="76" uniqueCount="40">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="72" uniqueCount="39">
   <si>
     <t>Part report</t>
   </si>
@@ -131,9 +131,6 @@
   </si>
   <si>
     <t>A5</t>
-  </si>
-  <si>
-    <t>A6</t>
   </si>
 </sst>
 </file>
@@ -970,7 +967,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet1"/>
-  <dimension ref="A1:H29"/>
+  <dimension ref="A1:H40"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="27.140625" customWidth="1"/>
@@ -998,7 +995,7 @@
         <v>23</v>
       </c>
       <c r="B4" s="1">
-        <v>46146</v>
+        <v>46330</v>
       </c>
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.25">
@@ -1006,7 +1003,7 @@
         <v>26</v>
       </c>
       <c r="B5" s="2">
-        <v>0.73836805555555562</v>
+        <v>0.7662268518518518</v>
       </c>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.25">
@@ -1400,32 +1397,16 @@
       </c>
     </row>
     <row r="28" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A28">
-        <v>13</v>
-      </c>
-      <c r="B28" s="7" t="s">
-        <v>39</v>
-      </c>
-      <c r="C28" s="7" t="s">
-        <v>25</v>
-      </c>
-      <c r="D28" s="7" t="s">
-        <v>20</v>
-      </c>
-      <c r="E28" s="7">
-        <v>94.46</v>
-      </c>
-      <c r="F28" s="7">
-        <v>0.3</v>
-      </c>
-      <c r="G28" s="7">
-        <v>-0.3</v>
-      </c>
-      <c r="H28" s="7" t="s">
-        <v>25</v>
-      </c>
+      <c r="B28" s="7"/>
+      <c r="C28" s="7"/>
+      <c r="D28" s="7"/>
+      <c r="E28" s="7"/>
+      <c r="F28" s="7"/>
+      <c r="G28" s="7"/>
+      <c r="H28" s="7"/>
     </row>
     <row r="29" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A29" s="7"/>
       <c r="B29" s="7"/>
       <c r="C29" s="7"/>
       <c r="D29" s="7"/>
@@ -1434,6 +1415,46 @@
       <c r="G29" s="7"/>
       <c r="H29" s="7"/>
     </row>
+    <row r="30" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A30" s="7"/>
+      <c r="B30" s="7"/>
+      <c r="C30" s="7"/>
+      <c r="D30" s="7"/>
+      <c r="E30" s="7"/>
+      <c r="F30" s="7"/>
+      <c r="G30" s="7"/>
+      <c r="H30" s="7"/>
+    </row>
+    <row r="31" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A31" s="7"/>
+    </row>
+    <row r="32" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A32" s="7"/>
+    </row>
+    <row r="33" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A33" s="7"/>
+    </row>
+    <row r="34" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A34" s="7"/>
+    </row>
+    <row r="35" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A35" s="7"/>
+    </row>
+    <row r="36" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A36" s="7"/>
+    </row>
+    <row r="37" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A37" s="7"/>
+    </row>
+    <row r="38" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A38" s="7"/>
+    </row>
+    <row r="39" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A39" s="7"/>
+    </row>
+    <row r="40" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A40" s="7"/>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
